--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.2184028598676</v>
+        <v>10.92299046472849</v>
       </c>
       <c r="D2" t="n">
-        <v>67.46714737162003</v>
+        <v>10.96341144788826</v>
       </c>
       <c r="E2" t="n">
-        <v>17.61350663809704</v>
+        <v>2.862194828690769</v>
       </c>
       <c r="F2" t="n">
-        <v>17.80091162660956</v>
+        <v>2.892648139324053</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.473865015961</v>
+        <v>11.77700306509366</v>
       </c>
       <c r="D3" t="n">
-        <v>72.8143090284815</v>
+        <v>11.83232521712825</v>
       </c>
       <c r="E3" t="n">
-        <v>17.61350663809704</v>
+        <v>2.862194828690769</v>
       </c>
       <c r="F3" t="n">
-        <v>17.80091162660956</v>
+        <v>2.892648139324053</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.02449126009887</v>
+        <v>7.478979829766066</v>
       </c>
       <c r="D4" t="n">
-        <v>46.48412974037726</v>
+        <v>7.553671082811306</v>
       </c>
       <c r="E4" t="n">
-        <v>17.61350663809704</v>
+        <v>2.862194828690769</v>
       </c>
       <c r="F4" t="n">
-        <v>17.80091162660956</v>
+        <v>2.892648139324053</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.26397028829503</v>
+        <v>4.592895171847943</v>
       </c>
       <c r="D5" t="n">
-        <v>27.99921813161383</v>
+        <v>4.549872946387247</v>
       </c>
       <c r="E5" t="n">
-        <v>17.61350663809704</v>
+        <v>2.862194828690769</v>
       </c>
       <c r="F5" t="n">
-        <v>17.80091162660956</v>
+        <v>2.892648139324053</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
